--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 8679-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44953</v>
+        <v>46066</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 8679-2026</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46066</v>
+        <v>45012</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45468</v>
+        <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46069</v>
+        <v>45012</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45012</v>
+        <v>46140</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1185,7 +1185,7 @@
         <v>45455</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1241,7 +1241,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1258,7 +1258,7 @@
         <v>44953</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46140</v>
+        <v>44953</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45468</v>
+        <v>45012</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -820,7 +820,7 @@
         <v>46066</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45012</v>
+        <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -966,7 +966,7 @@
         <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1039,7 +1039,7 @@
         <v>45012</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46140</v>
+        <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45455</v>
+        <v>45468</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1258,7 +1258,7 @@
         <v>44953</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44953</v>
+        <v>46140</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 8679-2026</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46066</v>
+        <v>45012</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 8679-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44953</v>
+        <v>46066</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46069</v>
+        <v>45012</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45012</v>
+        <v>46069</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1112,7 +1112,7 @@
         <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45468</v>
+        <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>44953</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>46140</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45468</v>
+        <v>45012</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45012</v>
+        <v>44953</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
         <v>46066</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45012</v>
+        <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46069</v>
+        <v>45468</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45455</v>
+        <v>46140</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44953</v>
+        <v>45012</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44953</v>
+        <v>45455</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46140</v>
+        <v>44953</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44953</v>
+        <v>45012</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 8679-2026</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46066</v>
+        <v>45012</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.1</v>
+        <v>0.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -966,7 +966,7 @@
         <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45468</v>
+        <v>45455</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46140</v>
+        <v>44953</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45012</v>
+        <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 8679-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45455</v>
+        <v>46066</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44953</v>
+        <v>46140</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>45012</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>45012</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>45455</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44953</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>46066</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>46140</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>45012</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45012</v>
+        <v>46069</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46069</v>
+        <v>45012</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 8679-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45455</v>
+        <v>46066</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44953</v>
+        <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1185,7 +1185,7 @@
         <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 8679-2026</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46066</v>
+        <v>44953</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1331,7 +1331,7 @@
         <v>46140</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45468</v>
+        <v>45012</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46069</v>
+        <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 8679-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45012</v>
+        <v>46066</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 8679-2026</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46066</v>
+        <v>45012</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1112,7 +1112,7 @@
         <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1185,7 +1185,7 @@
         <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44953</v>
+        <v>46069</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1331,7 +1331,7 @@
         <v>46140</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45468</v>
+        <v>45012</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44953</v>
+        <v>45012</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 8679-2026</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46066</v>
+        <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45012</v>
+        <v>45455</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 8679-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45455</v>
+        <v>46066</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1185,7 +1185,7 @@
         <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46069</v>
+        <v>44953</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1331,7 +1331,7 @@
         <v>46140</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45468</v>
+        <v>45012</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 8679-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45012</v>
+        <v>46066</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45012</v>
+        <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -966,7 +966,7 @@
         <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45455</v>
+        <v>45468</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 8679-2026</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46066</v>
+        <v>46140</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44953</v>
+        <v>45012</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44953</v>
+        <v>45455</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46140</v>
+        <v>44953</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45012</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46066</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>45468</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>46140</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>45012</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>45455</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>44953</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45012</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46066</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>45468</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>46140</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>45012</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>45455</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>44953</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 8679-2026</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46066</v>
+        <v>45012</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 8679-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44953</v>
+        <v>46066</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46069</v>
+        <v>45012</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45468</v>
+        <v>46069</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46140</v>
+        <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45012</v>
+        <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45455</v>
+        <v>44953</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44953</v>
+        <v>46140</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45468</v>
+        <v>45012</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45012</v>
+        <v>44953</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
         <v>46066</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>46069</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45455</v>
+        <v>45012</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44953</v>
+        <v>45455</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>44953</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>46140</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 25353-2022</t>
+          <t>A 25351-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -657,7 +657,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 25351-2022</t>
+          <t>A 25353-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -747,7 +747,7 @@
         <v>45012</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44953</v>
+        <v>45455</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 8679-2026</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46066</v>
+        <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45468</v>
+        <v>44953</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46069</v>
+        <v>45468</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1112,7 +1112,7 @@
         <v>45012</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 8679-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45455</v>
+        <v>46066</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44953</v>
+        <v>46069</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1331,7 +1331,7 @@
         <v>46140</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -584,7 +584,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A 25351-2022</t>
+          <t>A 25353-2022</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.8</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -657,7 +657,7 @@
     <row r="3" ht="15" customHeight="1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>A 25353-2022</t>
+          <t>A 25351-2022</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -687,7 +687,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.5</v>
+        <v>2.8</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -747,7 +747,7 @@
         <v>45012</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 8679-2026</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45455</v>
+        <v>46066</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
         <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44953</v>
+        <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1039,7 +1039,7 @@
         <v>45468</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45012</v>
+        <v>46140</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 8679-2026</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46066</v>
+        <v>45012</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46069</v>
+        <v>45455</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46140</v>
+        <v>44953</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -820,7 +820,7 @@
         <v>46066</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44953</v>
+        <v>45012</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46069</v>
+        <v>45012</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45468</v>
+        <v>46069</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46140</v>
+        <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45012</v>
+        <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45455</v>
+        <v>44953</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1314,7 +1314,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1328,10 +1328,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44953</v>
+        <v>46140</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46066</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>45012</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45012</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>46069</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44953</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>46140</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>46066</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>45012</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45012</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>46069</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>44953</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>46140</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE12"/>
+  <dimension ref="A1:AE11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45468</v>
+        <v>45012</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 8679-2026</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>46066</v>
+        <v>44953</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45012</v>
+        <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46069</v>
+        <v>45012</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1112,7 +1112,7 @@
         <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44953</v>
+        <v>46140</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1238,7 +1238,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr"/>
     </row>
-    <row r="11" ht="15" customHeight="1">
+    <row r="11">
       <c r="A11" t="inlineStr">
         <is>
           <t>A 4159-2023</t>
@@ -1258,7 +1258,7 @@
         <v>44953</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1310,79 +1310,6 @@
         <v>0</v>
       </c>
       <c r="V11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>A 20536-2026</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46140</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>SKÅNE LÄN</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>ÅSTORP</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44953</v>
+        <v>45012</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45468</v>
+        <v>46069</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46069</v>
+        <v>45012</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45012</v>
+        <v>46140</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1112,7 +1112,7 @@
         <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46140</v>
+        <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>44953</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45468</v>
+        <v>45012</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46069</v>
+        <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45012</v>
+        <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46140</v>
+        <v>45012</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1112,7 +1112,7 @@
         <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1185,7 +1185,7 @@
         <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44953</v>
+        <v>46140</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45468</v>
+        <v>45012</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44953</v>
+        <v>45012</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46069</v>
+        <v>45455</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45012</v>
+        <v>46069</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45455</v>
+        <v>44953</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1185,7 +1185,7 @@
         <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>46140</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45468</v>
+        <v>44953</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>45012</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45455</v>
+        <v>44953</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46069</v>
+        <v>45012</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44953</v>
+        <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44953</v>
+        <v>46069</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>46140</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>44953</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>45468</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>45012</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>44953</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>45012</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>46069</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>46140</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>44953</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>45468</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>45012</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>44953</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>45012</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>46069</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>46140</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44953</v>
+        <v>46140</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -820,7 +820,7 @@
         <v>45468</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45012</v>
+        <v>46069</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44953</v>
+        <v>45012</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1039,7 +1039,7 @@
         <v>45012</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1112,7 +1112,7 @@
         <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46069</v>
+        <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46140</v>
+        <v>44953</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>46140</v>
+        <v>45012</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45468</v>
+        <v>44953</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46069</v>
+        <v>45468</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45012</v>
+        <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1039,7 +1039,7 @@
         <v>45012</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1112,7 +1112,7 @@
         <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1185,7 +1185,7 @@
         <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44953</v>
+        <v>46140</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45012</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44953</v>
+        <v>45468</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45468</v>
+        <v>45012</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45012</v>
+        <v>45455</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45455</v>
+        <v>44953</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1185,7 +1185,7 @@
         <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>46140</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45012</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>45468</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45012</v>
+        <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -966,7 +966,7 @@
         <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45455</v>
+        <v>45012</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44953</v>
+        <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1185,7 +1185,7 @@
         <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>46140</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45468</v>
+        <v>45012</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44953</v>
+        <v>46069</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46069</v>
+        <v>45012</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45012</v>
+        <v>45455</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45455</v>
+        <v>44953</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1185,7 +1185,7 @@
         <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>46140</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>45012</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>46069</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45012</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>45455</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44953</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>46140</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>45012</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>46069</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>45012</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>45455</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44953</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>46140</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45468</v>
+        <v>45012</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45012</v>
+        <v>44953</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
         <v>46069</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45455</v>
+        <v>45012</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44953</v>
+        <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44953</v>
+        <v>46140</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46140</v>
+        <v>44953</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44953</v>
+        <v>45012</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46069</v>
+        <v>45012</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45468</v>
+        <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45012</v>
+        <v>45455</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45455</v>
+        <v>46140</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46140</v>
+        <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>44953</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45468</v>
+        <v>45012</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45012</v>
+        <v>44953</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -966,7 +966,7 @@
         <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45455</v>
+        <v>45012</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46140</v>
+        <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44953</v>
+        <v>46140</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1258,7 +1258,7 @@
         <v>44953</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45012</v>
+        <v>45455</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -820,7 +820,7 @@
         <v>44953</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45468</v>
+        <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46069</v>
+        <v>45468</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45012</v>
+        <v>46069</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45455</v>
+        <v>46140</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46140</v>
+        <v>45012</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44953</v>
+        <v>45012</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45455</v>
+        <v>45012</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44953</v>
+        <v>45455</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -893,7 +893,7 @@
         <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45468</v>
+        <v>46140</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46069</v>
+        <v>45012</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46140</v>
+        <v>44953</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45012</v>
+        <v>46069</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45012</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>45455</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>46140</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>45012</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44953</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>46069</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>45468</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -747,7 +747,7 @@
         <v>45012</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -820,7 +820,7 @@
         <v>45455</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
         <v>46140</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>45012</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1112,7 +1112,7 @@
         <v>44953</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1185,7 +1185,7 @@
         <v>46069</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1258,7 +1258,7 @@
         <v>45468</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45455</v>
+        <v>45012</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44953</v>
+        <v>46140</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46140</v>
+        <v>45012</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45012</v>
+        <v>46069</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44953</v>
+        <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46069</v>
+        <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45468</v>
+        <v>44953</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45468</v>
+        <v>44953</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -820,7 +820,7 @@
         <v>45012</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46140</v>
+        <v>45468</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45012</v>
+        <v>46140</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>46069</v>
+        <v>45012</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1112,7 +1112,7 @@
         <v>45455</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1185,7 +1185,7 @@
         <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44953</v>
+        <v>46069</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>44953</v>
+        <v>45455</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45012</v>
+        <v>44953</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45468</v>
+        <v>44953</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46140</v>
+        <v>46069</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45012</v>
+        <v>45468</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45455</v>
+        <v>46140</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44953</v>
+        <v>45012</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46069</v>
+        <v>45012</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>0.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>

--- a/Översikt ÅSTORP.xlsx
+++ b/Översikt ÅSTORP.xlsx
@@ -601,7 +601,7 @@
         <v>44732</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -674,7 +674,7 @@
         <v>44732</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     <row r="4" ht="15" customHeight="1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A 23798-2024</t>
+          <t>A 26262-2024</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -744,10 +744,10 @@
         </is>
       </c>
       <c r="D4" s="1" t="n">
-        <v>45455</v>
+        <v>45468</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
@@ -803,7 +803,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 4156-2023</t>
+          <t>A 14517-2023</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44953</v>
+        <v>45012</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -833,7 +833,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -876,7 +876,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 4159-2023</t>
+          <t>A 14516-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -890,10 +890,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44953</v>
+        <v>45012</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 8929-2026</t>
+          <t>A 23798-2024</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>46069</v>
+        <v>45455</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1022,7 +1022,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 26262-2024</t>
+          <t>A 4156-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45468</v>
+        <v>44953</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1052,7 +1052,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1095,7 +1095,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 20536-2026</t>
+          <t>A 8929-2026</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1109,10 +1109,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>46140</v>
+        <v>46069</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1168,7 +1168,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 14517-2023</t>
+          <t>A 4159-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45012</v>
+        <v>44953</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1241,7 +1241,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 14516-2023</t>
+          <t>A 20536-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45012</v>
+        <v>46140</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
